--- a/Daily_Task_Tracker.xlsx
+++ b/Daily_Task_Tracker.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Daily Tasks" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Daily Tasks'!A1:H24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Daily Tasks'!A1:H33</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,15 +400,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H33"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="60.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="56.83203125" customWidth="1"/>
-    <col min="7" max="7" width="34.83203125" customWidth="1"/>
+    <col min="6" max="6" width="58.83203125" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
     <col min="8" max="8" width="58.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -975,13 +975,13 @@
         <v>???</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>Event Interact ?????????????</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>?</v>
       </c>
       <c r="H22" t="str">
-        <v>?????????????????????</v>
+        <v>????????? UI</v>
       </c>
     </row>
     <row r="23">
@@ -1001,13 +1001,13 @@
         <v>???</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>Event Interact ?????????????</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>?</v>
       </c>
       <c r="H23" t="str">
-        <v>??????????? E ?????</v>
+        <v>????????? UI</v>
       </c>
     </row>
     <row r="24">
@@ -1027,19 +1027,253 @@
         <v>???</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>Event Interact ?????????????</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>?</v>
       </c>
       <c r="H24" t="str">
-        <v>?? -&gt; ?? -&gt; ???? -&gt; ???? -&gt; ????</v>
+        <v>????????? UI</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Day 8</v>
+      </c>
+      <c r="C25" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D25" t="str">
+        <v>?? WBP_InteractPrompt????? UI?</v>
+      </c>
+      <c r="E25" t="str">
+        <v>???</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>UI ????? E ??????????????</v>
+      </c>
+      <c r="H25" t="str">
+        <v>?????????</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Day 8</v>
+      </c>
+      <c r="C26" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D26" t="str">
+        <v>??????????????? UI ??</v>
+      </c>
+      <c r="E26" t="str">
+        <v>???</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>UI ????? E ??????????????</v>
+      </c>
+      <c r="H26" t="str">
+        <v>?????????</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Day 8</v>
+      </c>
+      <c r="C27" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D27" t="str">
+        <v>??????????????????</v>
+      </c>
+      <c r="E27" t="str">
+        <v>???</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>UI ????? E ??????????????</v>
+      </c>
+      <c r="H27" t="str">
+        <v>?????????</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Day 10</v>
+      </c>
+      <c r="C28" t="str">
+        <v>????</v>
+      </c>
+      <c r="D28" t="str">
+        <v>?? ItemCount????????</v>
+      </c>
+      <c r="E28" t="str">
+        <v>???</v>
+      </c>
+      <c r="F28" t="str">
+        <v>????? ItemCount ????</v>
+      </c>
+      <c r="G28" t="str">
+        <v>?</v>
+      </c>
+      <c r="H28" t="str">
+        <v>??????????</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Day 10</v>
+      </c>
+      <c r="C29" t="str">
+        <v>????</v>
+      </c>
+      <c r="D29" t="str">
+        <v>BP_InteractBox ?????????? +1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>???</v>
+      </c>
+      <c r="F29" t="str">
+        <v>BP_InteractBox ?? Cast To BP_ThirdPersonCharacter ?? AddItem</v>
+      </c>
+      <c r="G29" t="str">
+        <v>?</v>
+      </c>
+      <c r="H29" t="str">
+        <v>???????/??????? Cast</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Day 10</v>
+      </c>
+      <c r="C30" t="str">
+        <v>????</v>
+      </c>
+      <c r="D30" t="str">
+        <v>??????????????</v>
+      </c>
+      <c r="E30" t="str">
+        <v>???</v>
+      </c>
+      <c r="F30" t="str">
+        <v>BP_InteractBox ?? Cast To BP_ThirdPersonCharacter ?? AddItem</v>
+      </c>
+      <c r="G30" t="str">
+        <v>?</v>
+      </c>
+      <c r="H30" t="str">
+        <v>???????/??????? Cast</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Day 11</v>
+      </c>
+      <c r="C31" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D31" t="str">
+        <v>?? WBP_ItemHUD????? UI?</v>
+      </c>
+      <c r="E31" t="str">
+        <v>???</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>?? Item: 0???????</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Day 11</v>
+      </c>
+      <c r="C32" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D32" t="str">
+        <v>?? BeginPlay ?? ItemHUD ??????</v>
+      </c>
+      <c r="E32" t="str">
+        <v>???</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>?? InteractPromptWidget??????</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Day 11</v>
+      </c>
+      <c r="C33" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D33" t="str">
+        <v>AddItem ??? ItemHUD ?? ItemCount</v>
+      </c>
+      <c r="E33" t="str">
+        <v>???</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>?????? UI ? Item: 0 ?? Item: 1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H33"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H33"/>
   </ignoredErrors>
 </worksheet>
 </file>